--- a/artfynd/A 35964-2025 artfynd.xlsx
+++ b/artfynd/A 35964-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74245936</v>
       </c>
       <c r="B2" t="n">
-        <v>96970</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545065.5768781004</v>
+        <v>545066</v>
       </c>
       <c r="R2" t="n">
-        <v>6292305.218546995</v>
+        <v>6292305</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1987-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1987-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 35964-2025 artfynd.xlsx
+++ b/artfynd/A 35964-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74245936</v>
       </c>
       <c r="B2" t="n">
-        <v>99259</v>
+        <v>99264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35964-2025 artfynd.xlsx
+++ b/artfynd/A 35964-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74245936</v>
       </c>
       <c r="B2" t="n">
-        <v>99264</v>
+        <v>99265</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35964-2025 artfynd.xlsx
+++ b/artfynd/A 35964-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74245936</v>
       </c>
       <c r="B2" t="n">
-        <v>99265</v>
+        <v>99292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35964-2025 artfynd.xlsx
+++ b/artfynd/A 35964-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74245936</v>
       </c>
       <c r="B2" t="n">
-        <v>99292</v>
+        <v>99298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35964-2025 artfynd.xlsx
+++ b/artfynd/A 35964-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74245936</v>
       </c>
       <c r="B2" t="n">
-        <v>99298</v>
+        <v>99305</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35964-2025 artfynd.xlsx
+++ b/artfynd/A 35964-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74245936</v>
       </c>
       <c r="B2" t="n">
-        <v>99305</v>
+        <v>99309</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35964-2025 artfynd.xlsx
+++ b/artfynd/A 35964-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74245936</v>
       </c>
       <c r="B2" t="n">
-        <v>99309</v>
+        <v>99316</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35964-2025 artfynd.xlsx
+++ b/artfynd/A 35964-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74245936</v>
       </c>
       <c r="B2" t="n">
-        <v>99319</v>
+        <v>99324</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35964-2025 artfynd.xlsx
+++ b/artfynd/A 35964-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74245936</v>
       </c>
       <c r="B2" t="n">
-        <v>99324</v>
+        <v>99332</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35964-2025 artfynd.xlsx
+++ b/artfynd/A 35964-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74245936</v>
       </c>
       <c r="B2" t="n">
-        <v>99332</v>
+        <v>99342</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
